--- a/data_extactor/batch_10_fa/trimmed/batch_0016_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0016_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | شنیدن فعال | یادگیری فعال | استراتژی‌های یادگیری | نظارت</t>
+          <t>ریاضیات | درک مطلب | نگارش | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | مهندسی و فناوری | جغرافیا | رایانه و الکترونیک | طراحی | ساختمان و ساخت‌وساز | حقوق و امور دولتی</t>
+          <t>ریاضیات | مهندسی و فناوری | جغرافیا | رایانه و الکترونیک | طراحی | ساختمان و ساخت‌وساز | قانون و دولت</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | استدلال ریاضی | دید نزدیک | استدلال استقرایی | محاسبات عددی | تجسم فضایی</t>
+          <t>درک کتبی | استدلال قیاسی | استدلال ریاضی | بینایی نزدیک | استدلال استقرایی | توانایی عددی | تجسم</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ارزیابان و کارشناسان قیمت‌گذاری املاک | کارتوگراف‌ها و فتوگرامتریست‌ها | تکنسین‌ها و کاردان‌های مهندسی عمران | مهندسان عمران | کارشناسان متره، برآورد و آنالیز بها | مهندسان نقشه‌برداری ژئودزی | کاردان‌ها و تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان نقشه‌نگاری و فتوگرامتری | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | کارشناسان برآورد هزینه و مترورها | مهندسان نقشه‌برداری ژئودزی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم پایه | استراتژی‌های یادگیری</t>
+          <t>ریاضیات | درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال استقرایی | استدلال ریاضی | مرتب‌سازی اطلاعات | محاسبات عددی | تجسم فضایی</t>
+          <t>درک شفاهی | درک کتبی | استدلال استقرایی | استدلال ریاضی | ترتیب‌دهی اطلاعات | توانایی عددی | تجسم</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارتوگراف‌ها و فتوگرامتریست‌ها | تکنسین‌ها و کاردان‌های مهندسی عمران | جغرافیدانان | کاردان‌ها و تکنسین‌های سامانه‌های اطلاعات جغرافیایی GIS | کارشناسان و متخصصان سنجش از دور | کاردان‌ها و تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان نقشه‌برداری</t>
+          <t>کارشناسان نقشه‌نگاری و فتوگرامتری | کارشناسان و تکنسین‌های مهندسی عمران | جغرافیدانان | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | دانشمندان و فناوران سنجش از دور | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان نقشه‌برداری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | علوم پایه | درک مطلب | نگارش | سخن گفتن | ریاضیات | شنیدن فعال | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | علوم | درک مطلب | نگارش | سخن گفتن | ریاضیات | گوش دادن فعال | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | بیان کتبی | استدلال ریاضی</t>
+          <t>درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های فنی و عملیات مهندسی هوافضا | مکانیک‌ها و تعمیرکاران هواپیما | تکنسین‌های اویونیک و اویونیک پرواز | مهندسان صنایع | مهندسان ساخت و تولید | مهندسان مکانیک | مهندسان رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مکانیک و تکنسین خدمات هواپیما | تکنسین‌های اویونیک و الکترونیک پرواز | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان مکانیک | مهندسان رباتیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | ریاضیات | علوم پایه | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | ریاضیات | علوم | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | ریاضیات | زیست‌شناسی | مکانیک | تولیدات کشاورزی و دامی</t>
+          <t>مهندسی و فناوری | طراحی | ریاضیات | زیست‌شناسی | مکانیک | تولید مواد غذایی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های کشاورزی | تعمیرکاران و مکانیک‌های ماشین‌آلات و ادوات کشاورزی | کشاورزان، دامداران و مدیران مزارع و کشت و صنعت‌ها | مهندسان صنایع | تکنسین‌های کشاورزی دقیق | کارشناسان علوم خاک و گیاه‌پزشکی | متخصصان مدیریت منابع آب</t>
+          <t>تکنسین‌های کشاورزی | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | مدیران امور کشاورزی، دامپروری و شیلات | مهندسان صنایع | تکنسین‌های کشاورزی دقیق | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان و متخصصان مدیریت منابع آب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | علوم پایه | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | علوم | تفکر انتقادی | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بیوشیمیست‌ها و بیوفیزیکدانان | تکنسین‌ها و کاردان‌های زیست‌شناسی | مهندسان شیمی | تعمیرکاران و کارشناسان تعمیر تجهیزات پزشکی | تکنسین‌ها و کارشناسان آزمایشگاه‌های تشخیص طبی و بالینی | متخصصان زیست‌شناسی سلولی و مولکولی | مهندسان نانوسیستم‌ها</t>
+          <t>زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | تکنسین‌های علوم زیستی | مهندسان شیمی | تعمیرکاران تجهیزات پزشکی | کارشناسان علوم آزمایشگاهی بالینی | زیست‌شناسان سلولی و مولکولی | مهندسان نانوسیستم‌ها</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>علوم پایه | تفکر انتقادی | درک مطلب | یادگیری فعال | ریاضیات | سخن گفتن | شنیدن فعال | نگارش | نظارت</t>
+          <t>علوم | تفکر انتقادی | درک مطلب | یادگیری فعال | ریاضیات | سخن گفتن | گوش دادن فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای پالایشگاه و مجتمع‌های پتروشیمی | تکنسین‌ها و کاردان‌های شیمی | شیمیدانان | مهندسان صنایع | مهندسان متالورژی و مواد | مهندسان نفت</t>
+          <t>اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | تکنسین‌های شیمی | شیمی‌دانان | مهندسان صنایع | مهندسان متالورژی و مواد | مهندسان نفت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | ریاضیات | درک مطلب | علوم پایه | نظارت | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | ریاضیات | درک مطلب | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>طراحی | مهندسی و فناوری | ساختمان و ساخت‌وساز | ریاضیات | فیزیک | حقوق و امور دولتی | ایمنی و امنیت عمومی</t>
+          <t>طراحی | مهندسی و فناوری | ساختمان و ساخت‌وساز | ریاضیات | فیزیک | قانون و دولت | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | استدلال ریاضی</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>معماران، به‌جز معماری منظر و معماری دریایی | نقشه‌کش‌های معماری و عمران | تکنسین‌ها و کاردان‌های مهندسی عمران | مدیران پروژه‌های عمرانی و ساختمانی | بازرسان فنی ساختمان و سازه | مهندسان راه و ترابری و حمل‌ونقل | مهندسان آب و فاضلاب</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | نقشه‌کشان معماری و عمران | کارشناسان و تکنسین‌های مهندسی عمران | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | مهندسان حمل‌ونقل و ترافیک | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | ریاضیات | شنیدن فعال | نظارت | یادگیری فعال | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | ریاضیات | گوش دادن فعال | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | حمل‌ونقل | ساختمان و ساخت‌وساز | ریاضیات | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
+          <t>مهندسی و فناوری | طراحی | حمل و نقل | ساختمان و ساخت‌وساز | ریاضیات | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال ریاضی | مرتب‌سازی اطلاعات</t>
+          <t>استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال ریاضی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های عمرانی و ساختمانی | مهندسان صنایع | تکنسین‌های ترافیک و حمل‌ونقل | کارشناسان برنامه‌ریزی حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | مهندسان صنایع | تکنسین‌های ترافیک | برنامه‌ریزان سیستم‌های حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نگارش | درک مطلب | شنیدن فعال | ریاضیات | سخن گفتن | نظارت | علوم پایه | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | نگارش | درک مطلب | گوش دادن فعال | ریاضیات | سخن گفتن | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | مهندسان عمران | مهندسان محیط زیست | تکنسین‌های هیدرولوژی (آب‌شناسی) | هیدرولوژیست‌ها (متخصصان منابع آب) | متخصصان مدیریت منابع آب | اپراتورها و کارشناسان بهره‌برداری تصفیه‌خانه‌های آب و فاضلاب</t>
+          <t>مهندسان شیمی | مهندسان عمران | مهندسان محیط‌زیست | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | کارشناسان و متخصصان مدیریت منابع آب | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | طراحی | زبان انگلیسی | فیزیک | مخابرات و ارتباطات</t>
+          <t>رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | طراحی | زبان انگلیسی | فیزیک | مخابرات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله | بیان کتبی</t>
+          <t>درک شفاهی | درک کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | بیان کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سیستم‌های کامپیوتری | مهندسان برق | تکنسین‌ها و کاردان‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان مکاترونیک | توسعه‌دهندگان نرم‌افزار</t>
+          <t>تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان مکاترونیک | توسعه‌دهندگان نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
